--- a/docs/modele-import/modele-import-ifspa.xlsx
+++ b/docs/modele-import/modele-import-ifspa.xlsx
@@ -111,6 +111,15 @@
     <t>Adresse</t>
   </si>
   <si>
+    <t>Tuteur</t>
+  </si>
+  <si>
+    <t>Téléphone tuteur</t>
+  </si>
+  <si>
+    <t>Profession tuteur</t>
+  </si>
+  <si>
     <t>Filière *</t>
   </si>
   <si>
@@ -144,6 +153,12 @@
     <t>En texte, ex. 034 12 345 67.</t>
   </si>
   <si>
+    <t>Nom du tuteur, facultatif. Obligatoire si son téléphone ou sa profession est rempli.</t>
+  </si>
+  <si>
+    <t>En texte, ex. 033 12 345 67.</t>
+  </si>
+  <si>
     <t>Code de la filière : IF ou SF.</t>
   </si>
   <si>
@@ -183,6 +198,15 @@
     <t>Lot II A 12 Tanambao V</t>
   </si>
   <si>
+    <t>RAKOTO Jean</t>
+  </si>
+  <si>
+    <t>033 12 345 67</t>
+  </si>
+  <si>
+    <t>Commerçant</t>
+  </si>
+  <si>
     <t>IF</t>
   </si>
   <si>
@@ -244,6 +268,15 @@
   </si>
   <si>
     <t>Morarano</t>
+  </si>
+  <si>
+    <t>RASOA Marie</t>
+  </si>
+  <si>
+    <t>034 98 765 43</t>
+  </si>
+  <si>
+    <t>Institutrice</t>
   </si>
   <si>
     <t>2024</t>
@@ -525,11 +558,14 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,171 +611,206 @@
       <c r="N1" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>44</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" t="s">
-        <v>56</v>
+        <v>60</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="L3" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+      <c r="O3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H4" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="M4" t="s">
+        <v>75</v>
+      </c>
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
         <v>65</v>
       </c>
-      <c r="I4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N4" t="s">
-        <v>47</v>
+      <c r="Q4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" t="s">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="L5" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="M5" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>87</v>
+      </c>
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -760,105 +831,105 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/docs/modele-import/modele-import-ifspa.xlsx
+++ b/docs/modele-import/modele-import-ifspa.xlsx
@@ -8,7 +8,6 @@
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Lisez-moi"/>
     <sheet r:id="rId2" sheetId="2" name="Étudiants"/>
-    <sheet r:id="rId3" sheetId="3" name="Paiements"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -24,9 +23,6 @@
     <t>Feuille « Étudiants » : une ligne par étudiant inscrit en 2026-2027.</t>
   </si>
   <si>
-    <t>Feuille « Paiements » : une ligne par paiement déjà reçu pour 2026-2027 (droits et mensualités). Les impayés des années précédentes ne sont pas repris.</t>
-  </si>
-  <si>
     <t>Les colonnes marquées * sont obligatoires. Ne renommez pas les colonnes ; la ligne d'aide (ligne 2) peut rester ou être supprimée.</t>
   </si>
   <si>
@@ -45,13 +41,10 @@
     <t>Saisie dans Excel :</t>
   </si>
   <si>
-    <t>• téléphone et n° de reçu papier en texte (cellule au format Texte, ou valeur précédée d'une apostrophe : '0412) : sinon Excel retire le 0 initial ;</t>
-  </si>
-  <si>
-    <t>• dates au format JJ/MM/AAAA ; montants en ariary, nombres entiers sans « Ar » ;</t>
-  </si>
-  <si>
-    <t>• Mobile Money : l'opérateur est obligatoire ; sans référence, le paiement est accepté avec un avertissement.</t>
+    <t>• téléphones et CIN en texte (cellule au format Texte, ou valeur précédée d'une apostrophe : '0341234567) : sinon Excel retire le 0 initial ;</t>
+  </si>
+  <si>
+    <t>• dates au format JJ/MM/AAAA.</t>
   </si>
   <si>
     <t>Ce que fait l'import :</t>
@@ -63,10 +56,7 @@
     <t>• chaque étudiant est inscrit sur 2026-2027 seulement, au niveau indiqué : droits d'inscription + 10 mensualités (octobre à juillet), d'après les tarifs de Paramètres ;</t>
   </si>
   <si>
-    <t>• chaque paiement est réparti comme au guichet, de l'échéance la plus ancienne à la plus récente ; un montant au-delà du reste dû est refusé ;</t>
-  </si>
-  <si>
-    <t>• chaque paiement reçoit un reçu R-…, daté du jour indiqué ; le n° du reçu papier est gardé en observation ;</t>
+    <t>• les paiements ne sont pas repris : tout l'écolage de 2026-2027 est dû, rien n'est dû sur les années précédentes. Un paiement déjà reçu s'encaisse au guichet ;</t>
   </si>
   <si>
     <t>• rien n'est enregistré avant votre validation : un rapport liste d'abord les lignes acceptées et refusées, avec la raison ;</t>
@@ -75,13 +65,13 @@
     <t>• un fichier qui contient une erreur n'importe rien : corrigez-le et déposez-le à nouveau ;</t>
   </si>
   <si>
-    <t>• un étudiant déjà présent (mêmes nom, prénoms et date de naissance) n'est pas recréé ; un paiement déjà importé ne l'est pas deux fois ;</t>
-  </si>
-  <si>
-    <t>• un import ne s'annule pas : un paiement importé à tort s'annule comme les autres, dans Paiements.</t>
-  </si>
-  <si>
-    <t>Version CSV : enregistrez chaque feuille séparément (« CSV UTF-8 », séparateur point-virgule), soit etudiants.csv et paiements.csv.</t>
+    <t>• un étudiant déjà présent (mêmes nom, prénoms et date de naissance) n'est pas recréé : le même fichier peut être déposé deux fois ;</t>
+  </si>
+  <si>
+    <t>• un import ne s'annule pas : vérifiez le rapport avant de le lancer.</t>
+  </si>
+  <si>
+    <t>Version CSV : enregistrez la feuille « Étudiants » au format « CSV UTF-8 » (séparateur point-virgule), soit etudiants.csv.</t>
   </si>
   <si>
     <t>N° *</t>
@@ -132,10 +122,7 @@
     <t>Redoublant</t>
   </si>
   <si>
-    <t>Droits en</t>
-  </si>
-  <si>
-    <t>Numéro de ligne, unique. Sert à rattacher les paiements.</t>
+    <t>Numéro de ligne, unique. Fixe l'ordre des matricules.</t>
   </si>
   <si>
     <t>En majuscules ou non, il sera mis en majuscules.</t>
@@ -171,9 +158,6 @@
     <t>oui ou non (non par défaut).</t>
   </si>
   <si>
-    <t>Droits d'inscription payés en 1, 2 ou 3 fois (1 par défaut).</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -216,39 +200,39 @@
     <t>non</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RASOANAIVO</t>
+  </si>
+  <si>
+    <t>Fanja</t>
+  </si>
+  <si>
+    <t>02/11/2005</t>
+  </si>
+  <si>
+    <t>Fénérive-Est</t>
+  </si>
+  <si>
+    <t>501 011 012 345</t>
+  </si>
+  <si>
+    <t>032 98 765 43</t>
+  </si>
+  <si>
+    <t>Ankirihiry</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RASOANAIVO</t>
-  </si>
-  <si>
-    <t>Fanja</t>
-  </si>
-  <si>
-    <t>02/11/2005</t>
-  </si>
-  <si>
-    <t>Fénérive-Est</t>
-  </si>
-  <si>
-    <t>501 011 012 345</t>
-  </si>
-  <si>
-    <t>032 98 765 43</t>
-  </si>
-  <si>
-    <t>Ankirihiry</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
     <t>ANDRIAMAHEFA</t>
   </si>
   <si>
@@ -283,81 +267,6 @@
   </si>
   <si>
     <t>oui</t>
-  </si>
-  <si>
-    <t>N° étudiant *</t>
-  </si>
-  <si>
-    <t>Date *</t>
-  </si>
-  <si>
-    <t>Montant (Ar) *</t>
-  </si>
-  <si>
-    <t>Mode *</t>
-  </si>
-  <si>
-    <t>Opérateur</t>
-  </si>
-  <si>
-    <t>Référence</t>
-  </si>
-  <si>
-    <t>N° reçu papier</t>
-  </si>
-  <si>
-    <t>Le N° de l'étudiant dans la feuille Étudiants.</t>
-  </si>
-  <si>
-    <t>Nombre entier, sans espaces ni « Ar ».</t>
-  </si>
-  <si>
-    <t>Espèces ou Mobile Money.</t>
-  </si>
-  <si>
-    <t>Mobile Money seulement : MVola, Orange Money ou Airtel Money.</t>
-  </si>
-  <si>
-    <t>Mobile Money seulement : référence de la transaction.</t>
-  </si>
-  <si>
-    <t>En texte : numéro du reçu remis à l'époque, gardé pour mémoire.</t>
-  </si>
-  <si>
-    <t>05/10/2026</t>
-  </si>
-  <si>
-    <t>34000</t>
-  </si>
-  <si>
-    <t>Espèces</t>
-  </si>
-  <si>
-    <t>0412</t>
-  </si>
-  <si>
-    <t>80000</t>
-  </si>
-  <si>
-    <t>Mobile Money</t>
-  </si>
-  <si>
-    <t>MVola</t>
-  </si>
-  <si>
-    <t>MP261005.1432.A12345</t>
-  </si>
-  <si>
-    <t>0413</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
-  </si>
-  <si>
-    <t>180000</t>
-  </si>
-  <si>
-    <t>0420</t>
   </si>
 </sst>
 </file>
@@ -448,12 +357,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="s">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="s">
         <v>5</v>
@@ -464,12 +373,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="s">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="s">
         <v>8</v>
@@ -480,17 +389,17 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="s">
         <v>12</v>
@@ -521,25 +430,10 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -565,371 +459,236 @@
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
         <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M3" t="s">
         <v>58</v>
       </c>
-      <c r="I3" t="s">
+      <c r="N3" t="s">
         <v>59</v>
       </c>
-      <c r="J3" t="s">
+      <c r="O3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s">
         <v>60</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" t="s">
-        <v>64</v>
-      </c>
-      <c r="O3" t="s">
-        <v>52</v>
-      </c>
-      <c r="P3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
+      <c r="I4" t="s">
         <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I4" t="s">
-        <v>74</v>
       </c>
       <c r="K4" s="4"/>
       <c r="M4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="P4" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" t="s">
         <v>82</v>
       </c>
-      <c r="I5" t="s">
+      <c r="O5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" t="s">
         <v>83</v>
-      </c>
-      <c r="J5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="L5" t="s">
-        <v>86</v>
-      </c>
-      <c r="M5" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" t="s">
-        <v>67</v>
-      </c>
-      <c r="P5" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F4" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
